--- a/tomorrowcities/assets/data/sample_input_expert_mode/sample_distribution_file.xlsx
+++ b/tomorrowcities/assets/data/sample_input_expert_mode/sample_distribution_file.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eo\Desktop\expo_data_generator\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eo\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99B2D07-3725-430A-BC1C-639DDD909997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C808F0-E6CD-40A5-8B4D-745AAE2A736E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4230" yWindow="1125" windowWidth="21210" windowHeight="12810" activeTab="3" xr2:uid="{A146494A-A828-46F3-BEA3-7695A60C34FA}"/>
+    <workbookView xWindow="2490" yWindow="240" windowWidth="24255" windowHeight="14610" xr2:uid="{A146494A-A828-46F3-BEA3-7695A60C34FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="7" r:id="rId1"/>
@@ -77,12 +77,6 @@
     <t>Table 7</t>
   </si>
   <si>
-    <t>No. of commercial buildings per 1000 individuals</t>
-  </si>
-  <si>
-    <t>No. of industrial buildings per 1000 individuals</t>
-  </si>
-  <si>
     <t>AC (commercial)</t>
   </si>
   <si>
@@ -200,12 +194,6 @@
     <t>Replacement Cost (Unit Cost)</t>
   </si>
   <si>
-    <t>Low Income A</t>
-  </si>
-  <si>
-    <t>Low Income B</t>
-  </si>
-  <si>
     <t>Mid Income</t>
   </si>
   <si>
@@ -245,30 +233,15 @@
     <t>Unit price for replacement</t>
   </si>
   <si>
-    <t>Area constraints in percentage (AC) for industrial and commercial zones. Total built-up areas in these zones cannot exceed (AC*available area)</t>
-  </si>
-  <si>
     <t>Building footprint range</t>
   </si>
   <si>
-    <t>LIA</t>
-  </si>
-  <si>
-    <t>LIB</t>
-  </si>
-  <si>
     <t>MI</t>
   </si>
   <si>
     <t>HI</t>
   </si>
   <si>
-    <t>Low IncomeA (LIA) zone</t>
-  </si>
-  <si>
-    <t>Low IncomeB (LIB) zone</t>
-  </si>
-  <si>
     <t>Medium Income (MI) zone</t>
   </si>
   <si>
@@ -651,6 +624,34 @@
   </si>
   <si>
     <t>0.20, 0.30, 0.50</t>
+  </si>
+  <si>
+    <t>Low IncomeB (LI) zone</t>
+  </si>
+  <si>
+    <t>Very Low Income (VLI) zone</t>
+  </si>
+  <si>
+    <t>VLI</t>
+  </si>
+  <si>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>Number of commercial buildings per 1000 individuals</t>
+  </si>
+  <si>
+    <t>Number of industrial buildings per 1000 individuals</t>
+  </si>
+  <si>
+    <t>Area constraints in percentage (AC) for industrial and commercial zones. 
+Total built-up areas in these zones cannot exceed (AC*available area)</t>
+  </si>
+  <si>
+    <t>Very Low Income</t>
+  </si>
+  <si>
+    <t>Low Income</t>
   </si>
 </sst>
 </file>
@@ -692,16 +693,16 @@
     </font>
     <font>
       <b/>
-      <sz val="24"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color theme="5" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="5" tint="-0.499984740745262"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -733,7 +734,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -743,9 +744,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -827,26 +825,32 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1166,143 +1170,143 @@
   <dimension ref="A1:A27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="104.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="98.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="104.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>119</v>
+    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="40" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1317,33 +1321,33 @@
   <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="42.140625" style="9" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="9"/>
+    <col min="1" max="1" width="11.28515625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="42.140625" style="8" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="A1" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
+      <c r="A3" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
-        <v>90</v>
+      <c r="A4" s="35" t="s">
+        <v>81</v>
       </c>
       <c r="B4" s="34"/>
       <c r="C4" s="34"/>
@@ -1354,62 +1358,62 @@
       <c r="H4" s="34"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="16"/>
+      <c r="A5" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>51</v>
+      <c r="A6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>47</v>
+      <c r="A7" s="8" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
-        <v>158</v>
+      <c r="B8" s="5" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
-        <v>160</v>
+      <c r="B9" s="5" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
+      <c r="B10" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>48</v>
+      <c r="A11" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
+      <c r="A13" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
-        <v>91</v>
+      <c r="A14" s="35" t="s">
+        <v>82</v>
       </c>
       <c r="B14" s="34"/>
       <c r="C14" s="34"/>
@@ -1420,51 +1424,51 @@
       <c r="H14" s="34"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>51</v>
+      <c r="A16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>47</v>
+      <c r="A17" s="8" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
-        <v>97</v>
+      <c r="B18" s="8" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="9" t="s">
-        <v>96</v>
+      <c r="B19" s="8" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="9" t="s">
-        <v>98</v>
+      <c r="B20" s="8" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="9" t="s">
-        <v>94</v>
+      <c r="B21" s="8" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="9" t="s">
-        <v>95</v>
+      <c r="B22" s="8" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>48</v>
+      <c r="A23" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1486,324 +1490,324 @@
   <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="66.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="A1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
+      <c r="A2" s="9"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="7">
+        <v>202</v>
+      </c>
+      <c r="B3" s="6">
         <v>8</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="7">
+        <v>203</v>
+      </c>
+      <c r="B4" s="6">
         <v>2</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="6">
+        <v>15</v>
+      </c>
+      <c r="B7" s="5">
         <v>70</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="6">
+        <v>16</v>
+      </c>
+      <c r="B8" s="5">
         <v>70</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="9"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="6">
+        <v>17</v>
+      </c>
+      <c r="B10" s="5">
         <v>1000</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="6">
+        <v>18</v>
+      </c>
+      <c r="B11" s="5">
         <v>2000</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
+        <v>62</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="6">
+      <c r="A14" s="8"/>
+      <c r="B14" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="5">
         <v>40</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>40</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="5">
         <v>80</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
         <v>200</v>
       </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
+        <v>52</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="11"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>64</v>
+        <v>53</v>
+      </c>
+      <c r="B20" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="9"/>
-      <c r="B21" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" s="6">
+      <c r="A21" s="8"/>
+      <c r="B21" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="5">
         <v>10000</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <v>17500</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="5">
         <v>15000</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="5">
         <v>12500</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="5">
         <v>15000</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="5">
         <v>20000</v>
       </c>
     </row>
@@ -1845,17 +1849,17 @@
   <dimension ref="A1:M114"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.7109375" style="20" customWidth="1"/>
-    <col min="2" max="11" width="12.7109375" style="20" customWidth="1"/>
-    <col min="12" max="16384" width="8.7109375" style="20"/>
+    <col min="1" max="1" width="42.7109375" style="19" customWidth="1"/>
+    <col min="2" max="11" width="12.7109375" style="19" customWidth="1"/>
+    <col min="12" max="16384" width="8.7109375" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C1" s="34"/>
       <c r="D1" s="34"/>
@@ -1864,38 +1868,38 @@
       <c r="G1" s="34"/>
       <c r="H1" s="34"/>
     </row>
-    <row r="2" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-    </row>
-    <row r="3" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
-        <v>183</v>
-      </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
+    <row r="2" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+    </row>
+    <row r="3" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
-        <v>47</v>
+      <c r="A4" s="19" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
-        <v>34</v>
+      <c r="A5" s="19" t="s">
+        <v>32</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1911,79 +1915,79 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="21">
+      <c r="A6" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="20">
         <v>0.1</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="20">
         <v>0.2</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="20">
         <v>0.3</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="20">
         <v>0.4</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
-        <v>48</v>
+      <c r="A7" s="19" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
+      <c r="B9" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="B10" s="37"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
+      <c r="A10" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="33"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>74</v>
+        <v>201</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
+        <v>69</v>
+      </c>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
-        <v>47</v>
+      <c r="A12" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1991,699 +1995,699 @@
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="21">
+      <c r="A13" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="B13" s="20">
         <v>0.8</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="20">
         <v>0.2</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="20">
         <v>0</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="21">
+      <c r="A14" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" s="20">
         <v>0.8</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="20">
         <v>0.2</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="20">
         <v>0</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="21">
+      <c r="A15" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="20">
         <v>0</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="20">
         <v>0</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="20">
         <v>0.9</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" s="21">
+      <c r="A16" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="20">
         <v>0</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="20">
         <v>0</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="20">
         <v>0.1</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="20">
         <v>0.9</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
-        <v>48</v>
+      <c r="A17" s="19" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
+      <c r="B19" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="B20" s="37"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="23"/>
+      <c r="A20" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="B20" s="33"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
-        <v>47</v>
+      <c r="A22" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B23" s="21">
+      <c r="B23" s="20">
         <v>0.5</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="20">
         <v>0.45</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="20">
         <v>0.05</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
-        <v>48</v>
+      <c r="A24" s="19" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="38"/>
+      <c r="B26" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="37" t="s">
-        <v>198</v>
-      </c>
-      <c r="B27" s="37"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="37"/>
-      <c r="L27" s="37"/>
+      <c r="A27" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="E28" s="28" t="s">
-        <v>170</v>
-      </c>
-      <c r="F28" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="G28" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="H28" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="I28" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="J28" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="K28" s="28" t="s">
-        <v>176</v>
+      <c r="B28" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="F28" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="G28" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="H28" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="I28" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="J28" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="K28" s="27" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="C29" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="D29" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="E29" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="F29" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="G29" s="29" t="s">
+      <c r="B29" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="D29" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="H29" s="29" t="s">
+      <c r="E29" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="I29" s="29" t="s">
+      <c r="F29" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="J29" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="K29" s="29" t="s">
-        <v>181</v>
+      <c r="G29" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="H29" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="I29" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="J29" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="K29" s="28" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28"/>
-      <c r="K30" s="28"/>
+        <v>45</v>
+      </c>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="27"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="30">
+        <v>33</v>
+      </c>
+      <c r="B31" s="29">
         <v>0.1</v>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="29">
         <v>0.1</v>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="29">
         <v>0</v>
       </c>
-      <c r="E31" s="30">
+      <c r="E31" s="29">
         <v>0.1</v>
       </c>
-      <c r="F31" s="30">
+      <c r="F31" s="29">
         <v>0.25</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G31" s="29">
         <v>0.15</v>
       </c>
-      <c r="H31" s="30">
+      <c r="H31" s="29">
         <v>0.1</v>
       </c>
-      <c r="I31" s="30">
+      <c r="I31" s="29">
         <v>0.1</v>
       </c>
-      <c r="J31" s="30">
+      <c r="J31" s="29">
         <v>0.05</v>
       </c>
-      <c r="K31" s="30">
+      <c r="K31" s="29">
         <v>0.05</v>
       </c>
-      <c r="M31" s="31"/>
+      <c r="M31" s="30"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="30">
+        <v>21</v>
+      </c>
+      <c r="B32" s="29">
         <v>0.1</v>
       </c>
-      <c r="C32" s="30">
+      <c r="C32" s="29">
         <v>0</v>
       </c>
-      <c r="D32" s="30">
+      <c r="D32" s="29">
         <v>0.1</v>
       </c>
-      <c r="E32" s="30">
+      <c r="E32" s="29">
         <v>0.1</v>
       </c>
-      <c r="F32" s="30">
+      <c r="F32" s="29">
         <v>0.15</v>
       </c>
-      <c r="G32" s="30">
+      <c r="G32" s="29">
         <v>0.25</v>
       </c>
-      <c r="H32" s="30">
+      <c r="H32" s="29">
         <v>0.1</v>
       </c>
-      <c r="I32" s="30">
+      <c r="I32" s="29">
         <v>0.1</v>
       </c>
-      <c r="J32" s="30">
+      <c r="J32" s="29">
         <v>0.05</v>
       </c>
-      <c r="K32" s="30">
+      <c r="K32" s="29">
         <v>0.05</v>
       </c>
-      <c r="M32" s="31"/>
+      <c r="M32" s="30"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B33" s="30">
+        <v>181</v>
+      </c>
+      <c r="B33" s="29">
         <v>0.1</v>
       </c>
-      <c r="C33" s="30">
+      <c r="C33" s="29">
         <v>0</v>
       </c>
-      <c r="D33" s="30">
+      <c r="D33" s="29">
         <v>0.1</v>
       </c>
-      <c r="E33" s="30">
+      <c r="E33" s="29">
         <v>0.1</v>
       </c>
-      <c r="F33" s="30">
+      <c r="F33" s="29">
         <v>0.15</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G33" s="29">
         <v>0.25</v>
       </c>
-      <c r="H33" s="30">
+      <c r="H33" s="29">
         <v>0.1</v>
       </c>
-      <c r="I33" s="30">
+      <c r="I33" s="29">
         <v>0.1</v>
       </c>
-      <c r="J33" s="30">
+      <c r="J33" s="29">
         <v>0.05</v>
       </c>
-      <c r="K33" s="30">
+      <c r="K33" s="29">
         <v>0.05</v>
       </c>
-      <c r="M33" s="31"/>
+      <c r="M33" s="30"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
-        <v>48</v>
+      <c r="A34" s="19" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="B36" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
+      <c r="A36" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="B37" s="37"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="37"/>
-      <c r="K37" s="37"/>
-      <c r="L37" s="37"/>
+      <c r="A37" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="B37" s="33"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="33"/>
+      <c r="L37" s="33"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="C38" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="29"/>
+      <c r="B38" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="28"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
+        <v>45</v>
+      </c>
+      <c r="B39" s="27"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="27"/>
+      <c r="J39" s="27"/>
+      <c r="K39" s="27"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="32">
+      <c r="B40" s="31">
         <v>4</v>
       </c>
-      <c r="C40" s="32">
+      <c r="C40" s="31">
         <v>8</v>
       </c>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="20" t="s">
-        <v>48</v>
+      <c r="A41" s="19" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="B43" s="38" t="s">
-        <v>194</v>
-      </c>
-      <c r="C43" s="38"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
-      <c r="J43" s="38"/>
+      <c r="A43" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B43" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="B44" s="37"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="37"/>
-      <c r="I44" s="37"/>
-      <c r="J44" s="37"/>
-      <c r="K44" s="37"/>
-      <c r="L44" s="37"/>
+      <c r="A44" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="B44" s="33"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="33"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="33"/>
+      <c r="H44" s="33"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="33"/>
+      <c r="K44" s="33"/>
+      <c r="L44" s="33"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="C45" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="29"/>
-      <c r="I45" s="29"/>
-      <c r="J45" s="29"/>
-      <c r="K45" s="29"/>
+      <c r="B45" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="C45" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
+      <c r="J45" s="28"/>
+      <c r="K45" s="28"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
+        <v>45</v>
+      </c>
+      <c r="B46" s="27"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="27"/>
+      <c r="J46" s="27"/>
+      <c r="K46" s="27"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
-      <c r="B47" s="32">
+      <c r="B47" s="31">
         <v>5</v>
       </c>
-      <c r="C47" s="32">
+      <c r="C47" s="31">
         <v>10</v>
       </c>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="30"/>
-      <c r="K47" s="30"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="20" t="s">
-        <v>48</v>
+      <c r="A48" s="19" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="B50" s="38" t="s">
-        <v>200</v>
-      </c>
-      <c r="C50" s="38"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
-      <c r="I50" s="38"/>
-      <c r="J50" s="38"/>
+      <c r="A50" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="B51" s="37"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="37"/>
-      <c r="H51" s="37"/>
-      <c r="I51" s="37"/>
-      <c r="J51" s="37"/>
-      <c r="K51" s="37"/>
-      <c r="L51" s="37"/>
+      <c r="A51" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="B51" s="33"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="33"/>
+      <c r="E51" s="33"/>
+      <c r="F51" s="33"/>
+      <c r="G51" s="33"/>
+      <c r="H51" s="33"/>
+      <c r="I51" s="33"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="33"/>
+      <c r="L51" s="33"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
-      <c r="B52" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="C52" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
+      <c r="B52" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="C52" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53" s="28"/>
-      <c r="C53" s="28"/>
-      <c r="D53" s="28"/>
-      <c r="E53" s="28"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="28"/>
-      <c r="K53" s="28"/>
+        <v>45</v>
+      </c>
+      <c r="B53" s="27"/>
+      <c r="C53" s="27"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27"/>
+      <c r="I53" s="27"/>
+      <c r="J53" s="27"/>
+      <c r="K53" s="27"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="B54" s="32">
+      <c r="B54" s="31">
         <v>2</v>
       </c>
-      <c r="C54" s="32">
+      <c r="C54" s="31">
         <v>5</v>
       </c>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="30"/>
-      <c r="H54" s="30"/>
-      <c r="I54" s="30"/>
-      <c r="J54" s="30"/>
-      <c r="K54" s="30"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
+      <c r="I54" s="29"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="29"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="20" t="s">
-        <v>48</v>
+      <c r="A55" s="19" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B57" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="C57" s="38"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="38"/>
-      <c r="I57" s="38"/>
-      <c r="J57" s="38"/>
-      <c r="K57" s="38"/>
+      <c r="B57" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="32"/>
+      <c r="K57" s="32"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="23"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
-      <c r="H58" s="23"/>
-      <c r="I58" s="23"/>
-      <c r="J58" s="23"/>
-      <c r="K58" s="23"/>
+      <c r="A58" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="B58" s="33"/>
+      <c r="C58" s="33"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
+      <c r="J58" s="22"/>
+      <c r="K58" s="22"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="B59" s="37"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="23"/>
-      <c r="G59" s="23"/>
-      <c r="H59" s="23"/>
-      <c r="I59" s="23"/>
-      <c r="J59" s="23"/>
-      <c r="K59" s="23"/>
+      <c r="A59" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="B59" s="33"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
+      <c r="H59" s="22"/>
+      <c r="I59" s="22"/>
+      <c r="J59" s="22"/>
+      <c r="K59" s="22"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="19"/>
+      <c r="A60" s="18"/>
       <c r="B60" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G60" s="23"/>
-      <c r="H60" s="23"/>
-      <c r="I60" s="23"/>
-      <c r="J60" s="23"/>
-      <c r="K60" s="23"/>
+        <v>76</v>
+      </c>
+      <c r="G60" s="22"/>
+      <c r="H60" s="22"/>
+      <c r="I60" s="22"/>
+      <c r="J60" s="22"/>
+      <c r="K60" s="22"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="20" t="s">
-        <v>47</v>
+      <c r="A61" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -2697,93 +2701,93 @@
       <c r="K61" s="3"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B62" s="21">
+      <c r="A62" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B62" s="20">
         <v>0.05</v>
       </c>
-      <c r="C62" s="21">
+      <c r="C62" s="20">
         <v>0.15</v>
       </c>
-      <c r="D62" s="21">
+      <c r="D62" s="20">
         <v>0.4</v>
       </c>
-      <c r="E62" s="21">
+      <c r="E62" s="20">
         <v>0.3</v>
       </c>
-      <c r="F62" s="21">
+      <c r="F62" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B63" s="21">
+      <c r="A63" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B63" s="20">
         <v>0.15</v>
       </c>
-      <c r="C63" s="21">
+      <c r="C63" s="20">
         <v>0.25</v>
       </c>
-      <c r="D63" s="21">
+      <c r="D63" s="20">
         <v>0.3</v>
       </c>
-      <c r="E63" s="21">
+      <c r="E63" s="20">
         <v>0.25</v>
       </c>
-      <c r="F63" s="21">
+      <c r="F63" s="20">
         <v>0.05</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="B64" s="21">
+      <c r="A64" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B64" s="20">
         <v>0.05</v>
       </c>
-      <c r="C64" s="21">
+      <c r="C64" s="20">
         <v>0.15</v>
       </c>
-      <c r="D64" s="21">
+      <c r="D64" s="20">
         <v>0.4</v>
       </c>
-      <c r="E64" s="21">
+      <c r="E64" s="20">
         <v>0.3</v>
       </c>
-      <c r="F64" s="21">
+      <c r="F64" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="20" t="s">
-        <v>48</v>
+      <c r="A65" s="19" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B67" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="C67" s="38"/>
-      <c r="D67" s="38"/>
-      <c r="E67" s="38"/>
-      <c r="F67" s="38"/>
-      <c r="G67" s="38"/>
-      <c r="H67" s="38"/>
-      <c r="I67" s="38"/>
-      <c r="J67" s="38"/>
-      <c r="K67" s="38"/>
+      <c r="B67" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C67" s="32"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="32"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="32"/>
+      <c r="J67" s="32"/>
+      <c r="K67" s="32"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="B68" s="37"/>
-      <c r="C68" s="37"/>
+      <c r="A68" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="B68" s="33"/>
+      <c r="C68" s="33"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
@@ -2794,11 +2798,11 @@
       <c r="K68" s="3"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="B69" s="37"/>
-      <c r="C69" s="37"/>
+      <c r="A69" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" s="33"/>
+      <c r="C69" s="33"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
@@ -2809,13 +2813,13 @@
       <c r="K69" s="3"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="B70" s="37"/>
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="37"/>
+      <c r="A70" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="B70" s="33"/>
+      <c r="C70" s="33"/>
+      <c r="D70" s="33"/>
+      <c r="E70" s="33"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
@@ -2824,36 +2828,36 @@
       <c r="K70" s="3"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="B71" s="37"/>
-      <c r="C71" s="37"/>
-      <c r="D71" s="37"/>
-      <c r="E71" s="37"/>
-      <c r="F71" s="37"/>
-      <c r="G71" s="37"/>
-      <c r="H71" s="37"/>
-      <c r="I71" s="37"/>
-      <c r="J71" s="37"/>
-      <c r="K71" s="37"/>
-      <c r="L71" s="37"/>
+      <c r="A71" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="B71" s="33"/>
+      <c r="C71" s="33"/>
+      <c r="D71" s="33"/>
+      <c r="E71" s="33"/>
+      <c r="F71" s="33"/>
+      <c r="G71" s="33"/>
+      <c r="H71" s="33"/>
+      <c r="I71" s="33"/>
+      <c r="J71" s="33"/>
+      <c r="K71" s="33"/>
+      <c r="L71" s="33"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B72" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
@@ -2862,8 +2866,8 @@
       <c r="K72" s="3"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="20" t="s">
-        <v>47</v>
+      <c r="A73" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -2877,127 +2881,127 @@
       <c r="K73" s="3"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="20" t="s">
+      <c r="A74" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B74" s="20">
+        <v>0.7</v>
+      </c>
+      <c r="C74" s="20">
+        <v>0.7</v>
+      </c>
+      <c r="D74" s="20">
+        <v>0.7</v>
+      </c>
+      <c r="E74" s="20">
+        <v>0.8</v>
+      </c>
+      <c r="F74" s="20">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75" s="20">
+        <v>0.7</v>
+      </c>
+      <c r="C75" s="20">
+        <v>0.8</v>
+      </c>
+      <c r="D75" s="20">
+        <v>0.8</v>
+      </c>
+      <c r="E75" s="20">
+        <v>0.9</v>
+      </c>
+      <c r="F75" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B74" s="21">
-        <v>0.7</v>
-      </c>
-      <c r="C74" s="21">
-        <v>0.7</v>
-      </c>
-      <c r="D74" s="21">
-        <v>0.7</v>
-      </c>
-      <c r="E74" s="21">
+      <c r="B76" s="20">
         <v>0.8</v>
       </c>
-      <c r="F74" s="21">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="B75" s="21">
-        <v>0.7</v>
-      </c>
-      <c r="C75" s="21">
-        <v>0.8</v>
-      </c>
-      <c r="D75" s="21">
-        <v>0.8</v>
-      </c>
-      <c r="E75" s="21">
+      <c r="C76" s="20">
         <v>0.9</v>
       </c>
-      <c r="F75" s="21">
+      <c r="D76" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B76" s="21">
-        <v>0.8</v>
-      </c>
-      <c r="C76" s="21">
-        <v>0.9</v>
-      </c>
-      <c r="D76" s="21">
+      <c r="E76" s="20">
         <v>1</v>
       </c>
-      <c r="E76" s="21">
+      <c r="F76" s="20">
         <v>1</v>
       </c>
-      <c r="F76" s="21">
-        <v>1</v>
-      </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="20" t="s">
-        <v>48</v>
+      <c r="A77" s="19" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B79" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="C79" s="38"/>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="38"/>
-      <c r="H79" s="38"/>
-      <c r="I79" s="38"/>
-      <c r="J79" s="38"/>
-      <c r="K79" s="38"/>
-      <c r="L79" s="38"/>
+      <c r="B79" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="C79" s="32"/>
+      <c r="D79" s="32"/>
+      <c r="E79" s="32"/>
+      <c r="F79" s="32"/>
+      <c r="G79" s="32"/>
+      <c r="H79" s="32"/>
+      <c r="I79" s="32"/>
+      <c r="J79" s="32"/>
+      <c r="K79" s="32"/>
+      <c r="L79" s="32"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="B80" s="37"/>
-      <c r="C80" s="22"/>
-      <c r="D80" s="22"/>
-      <c r="E80" s="22"/>
-      <c r="F80" s="22"/>
-      <c r="G80" s="22"/>
-      <c r="H80" s="22"/>
-      <c r="I80" s="22"/>
-      <c r="J80" s="22"/>
-      <c r="K80" s="22"/>
-      <c r="L80" s="22"/>
+      <c r="A80" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="B80" s="33"/>
+      <c r="C80" s="21"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="21"/>
+      <c r="F80" s="21"/>
+      <c r="G80" s="21"/>
+      <c r="H80" s="21"/>
+      <c r="I80" s="21"/>
+      <c r="J80" s="21"/>
+      <c r="K80" s="21"/>
+      <c r="L80" s="21"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="24"/>
+      <c r="A81" s="23"/>
       <c r="B81" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E81" s="22"/>
-      <c r="F81" s="22"/>
-      <c r="G81" s="22"/>
-      <c r="H81" s="22"/>
-      <c r="I81" s="22"/>
-      <c r="J81" s="22"/>
-      <c r="K81" s="22"/>
-      <c r="L81" s="22"/>
+        <v>181</v>
+      </c>
+      <c r="E81" s="21"/>
+      <c r="F81" s="21"/>
+      <c r="G81" s="21"/>
+      <c r="H81" s="21"/>
+      <c r="I81" s="21"/>
+      <c r="J81" s="21"/>
+      <c r="K81" s="21"/>
+      <c r="L81" s="21"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="20" t="s">
-        <v>47</v>
+      <c r="A82" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -3012,87 +3016,87 @@
       <c r="L82" s="3"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B83" s="21">
+      <c r="B83" s="20">
         <v>0.25</v>
       </c>
-      <c r="C83" s="21">
+      <c r="C83" s="20">
         <v>0.7</v>
       </c>
-      <c r="D83" s="21">
+      <c r="D83" s="20">
         <v>0.05</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="20" t="s">
-        <v>48</v>
+      <c r="A84" s="19" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="8" t="s">
+      <c r="A86" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B86" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="C86" s="38"/>
-      <c r="D86" s="38"/>
-      <c r="E86" s="38"/>
-      <c r="F86" s="38"/>
-      <c r="G86" s="38"/>
-      <c r="H86" s="38"/>
-      <c r="I86" s="38"/>
-      <c r="J86" s="38"/>
+      <c r="B86" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C86" s="32"/>
+      <c r="D86" s="32"/>
+      <c r="E86" s="32"/>
+      <c r="F86" s="32"/>
+      <c r="G86" s="32"/>
+      <c r="H86" s="32"/>
+      <c r="I86" s="32"/>
+      <c r="J86" s="32"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="B87" s="37"/>
-      <c r="C87" s="37"/>
-      <c r="D87" s="22"/>
-      <c r="E87" s="22"/>
-      <c r="F87" s="22"/>
-      <c r="G87" s="22"/>
-      <c r="H87" s="22"/>
-      <c r="I87" s="22"/>
-      <c r="J87" s="22"/>
+      <c r="A87" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="B87" s="33"/>
+      <c r="C87" s="33"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="21"/>
+      <c r="F87" s="21"/>
+      <c r="G87" s="21"/>
+      <c r="H87" s="21"/>
+      <c r="I87" s="21"/>
+      <c r="J87" s="21"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="B88" s="37"/>
-      <c r="C88" s="37"/>
-      <c r="D88" s="37"/>
-      <c r="E88" s="37"/>
-      <c r="F88" s="37"/>
-      <c r="G88" s="37"/>
-      <c r="H88" s="37"/>
-      <c r="I88" s="37"/>
-      <c r="J88" s="37"/>
+      <c r="A88" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="B88" s="33"/>
+      <c r="C88" s="33"/>
+      <c r="D88" s="33"/>
+      <c r="E88" s="33"/>
+      <c r="F88" s="33"/>
+      <c r="G88" s="33"/>
+      <c r="H88" s="33"/>
+      <c r="I88" s="33"/>
+      <c r="J88" s="33"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="19"/>
+      <c r="A89" s="18"/>
       <c r="B89" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G89" s="22"/>
-      <c r="H89" s="22"/>
-      <c r="I89" s="22"/>
-      <c r="J89" s="22"/>
+        <v>83</v>
+      </c>
+      <c r="G89" s="21"/>
+      <c r="H89" s="21"/>
+      <c r="I89" s="21"/>
+      <c r="J89" s="21"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="20" t="s">
-        <v>47</v>
+      <c r="A90" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -3100,132 +3104,132 @@
       <c r="E90" s="3"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A91" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B91" s="21">
+      <c r="A91" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B91" s="20">
         <v>1</v>
       </c>
-      <c r="C91" s="21">
+      <c r="C91" s="20">
         <v>0</v>
       </c>
-      <c r="D91" s="21">
+      <c r="D91" s="20">
         <v>0</v>
       </c>
-      <c r="E91" s="21">
+      <c r="E91" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="B92" s="21">
+      <c r="A92" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B92" s="20">
         <v>0.9</v>
       </c>
-      <c r="C92" s="21">
+      <c r="C92" s="20">
         <v>0</v>
       </c>
-      <c r="D92" s="21">
+      <c r="D92" s="20">
         <v>0</v>
       </c>
-      <c r="E92" s="21">
+      <c r="E92" s="20">
         <v>0.1</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="B93" s="21">
+      <c r="A93" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B93" s="20">
         <v>0.8</v>
       </c>
-      <c r="C93" s="21">
+      <c r="C93" s="20">
         <v>0</v>
       </c>
-      <c r="D93" s="21">
+      <c r="D93" s="20">
         <v>0</v>
       </c>
-      <c r="E93" s="21">
+      <c r="E93" s="20">
         <v>0.2</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="B94" s="21">
+      <c r="A94" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B94" s="20">
         <v>0</v>
       </c>
-      <c r="C94" s="21">
+      <c r="C94" s="20">
         <v>0</v>
       </c>
-      <c r="D94" s="21">
+      <c r="D94" s="20">
         <v>1</v>
       </c>
-      <c r="E94" s="21">
+      <c r="E94" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="B95" s="21">
+      <c r="A95" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B95" s="20">
         <v>0</v>
       </c>
-      <c r="C95" s="21">
+      <c r="C95" s="20">
         <v>1</v>
       </c>
-      <c r="D95" s="21">
+      <c r="D95" s="20">
         <v>0</v>
       </c>
-      <c r="E95" s="21">
+      <c r="E95" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="20" t="s">
-        <v>48</v>
+      <c r="A96" s="19" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="8" t="s">
+      <c r="A98" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B98" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="C98" s="38"/>
-      <c r="D98" s="38"/>
-      <c r="E98" s="38"/>
-      <c r="F98" s="38"/>
-      <c r="G98" s="38"/>
-      <c r="H98" s="38"/>
-      <c r="I98" s="38"/>
+      <c r="B98" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C98" s="32"/>
+      <c r="D98" s="32"/>
+      <c r="E98" s="32"/>
+      <c r="F98" s="32"/>
+      <c r="G98" s="32"/>
+      <c r="H98" s="32"/>
+      <c r="I98" s="32"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="B99" s="37"/>
-      <c r="C99" s="22"/>
-      <c r="D99" s="22"/>
-      <c r="E99" s="22"/>
-      <c r="F99" s="22"/>
-      <c r="G99" s="22"/>
-      <c r="H99" s="22"/>
-      <c r="I99" s="22"/>
+      <c r="A99" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="B99" s="33"/>
+      <c r="C99" s="21"/>
+      <c r="D99" s="21"/>
+      <c r="E99" s="21"/>
+      <c r="F99" s="21"/>
+      <c r="G99" s="21"/>
+      <c r="H99" s="21"/>
+      <c r="I99" s="21"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B100" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
@@ -3234,8 +3238,8 @@
       <c r="I100" s="3"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="20" t="s">
-        <v>47</v>
+      <c r="A101" s="19" t="s">
+        <v>45</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -3247,106 +3251,106 @@
       <c r="I101" s="3"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B102" s="21">
+      <c r="B102" s="20">
         <v>0.4</v>
       </c>
-      <c r="C102" s="21">
+      <c r="C102" s="20">
         <v>0.75</v>
       </c>
-      <c r="D102" s="21">
+      <c r="D102" s="20">
         <v>0.8</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103" s="20" t="s">
-        <v>48</v>
+      <c r="A103" s="19" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" s="8" t="s">
+      <c r="A105" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B105" s="38" t="s">
+      <c r="B105" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C105" s="32"/>
+      <c r="D105" s="32"/>
+      <c r="E105" s="32"/>
+      <c r="F105" s="32"/>
+      <c r="G105" s="32"/>
+      <c r="H105" s="32"/>
+      <c r="I105" s="32"/>
+      <c r="J105" s="32"/>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A106" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="B106" s="33"/>
+      <c r="C106" s="33"/>
+      <c r="D106" s="24"/>
+      <c r="E106" s="24"/>
+      <c r="F106" s="24"/>
+      <c r="G106" s="24"/>
+      <c r="H106" s="24"/>
+      <c r="I106" s="24"/>
+      <c r="J106" s="24"/>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A107" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="B107" s="33"/>
+      <c r="C107" s="33"/>
+      <c r="D107" s="24"/>
+      <c r="E107" s="24"/>
+      <c r="F107" s="24"/>
+      <c r="G107" s="24"/>
+      <c r="H107" s="24"/>
+      <c r="I107" s="24"/>
+      <c r="J107" s="24"/>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A108" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B108" s="33"/>
+      <c r="C108" s="33"/>
+      <c r="D108" s="33"/>
+      <c r="E108" s="33"/>
+      <c r="F108" s="33"/>
+      <c r="G108" s="33"/>
+      <c r="H108" s="33"/>
+      <c r="I108" s="33"/>
+      <c r="J108" s="33"/>
+      <c r="K108" s="33"/>
+      <c r="L108" s="33"/>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" s="18"/>
+      <c r="B109" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G109" s="24"/>
+      <c r="H109" s="24"/>
+      <c r="I109" s="24"/>
+      <c r="J109" s="24"/>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" s="22" t="s">
         <v>45</v>
-      </c>
-      <c r="C105" s="38"/>
-      <c r="D105" s="38"/>
-      <c r="E105" s="38"/>
-      <c r="F105" s="38"/>
-      <c r="G105" s="38"/>
-      <c r="H105" s="38"/>
-      <c r="I105" s="38"/>
-      <c r="J105" s="38"/>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="B106" s="37"/>
-      <c r="C106" s="37"/>
-      <c r="D106" s="25"/>
-      <c r="E106" s="25"/>
-      <c r="F106" s="25"/>
-      <c r="G106" s="25"/>
-      <c r="H106" s="25"/>
-      <c r="I106" s="25"/>
-      <c r="J106" s="25"/>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="B107" s="37"/>
-      <c r="C107" s="37"/>
-      <c r="D107" s="25"/>
-      <c r="E107" s="25"/>
-      <c r="F107" s="25"/>
-      <c r="G107" s="25"/>
-      <c r="H107" s="25"/>
-      <c r="I107" s="25"/>
-      <c r="J107" s="25"/>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="B108" s="37"/>
-      <c r="C108" s="37"/>
-      <c r="D108" s="37"/>
-      <c r="E108" s="37"/>
-      <c r="F108" s="37"/>
-      <c r="G108" s="37"/>
-      <c r="H108" s="37"/>
-      <c r="I108" s="37"/>
-      <c r="J108" s="37"/>
-      <c r="K108" s="37"/>
-      <c r="L108" s="37"/>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="19"/>
-      <c r="B109" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G109" s="25"/>
-      <c r="H109" s="25"/>
-      <c r="I109" s="25"/>
-      <c r="J109" s="25"/>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="23" t="s">
-        <v>47</v>
       </c>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -3359,83 +3363,78 @@
       <c r="J110" s="3"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B111" s="21">
+      <c r="A111" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B111" s="20">
         <v>0</v>
       </c>
-      <c r="C111" s="21">
+      <c r="C111" s="20">
         <v>0</v>
       </c>
-      <c r="D111" s="21">
+      <c r="D111" s="20">
         <v>0.1</v>
       </c>
-      <c r="E111" s="21">
+      <c r="E111" s="20">
         <v>0.4</v>
       </c>
-      <c r="F111" s="21">
+      <c r="F111" s="20">
         <v>0.5</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B112" s="21">
+      <c r="A112" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B112" s="20">
         <v>0.05</v>
       </c>
-      <c r="C112" s="21">
+      <c r="C112" s="20">
         <v>0.15</v>
       </c>
-      <c r="D112" s="21">
+      <c r="D112" s="20">
         <v>0.35</v>
       </c>
-      <c r="E112" s="21">
+      <c r="E112" s="20">
         <v>0.25</v>
       </c>
-      <c r="F112" s="21">
+      <c r="F112" s="20">
         <v>0.2</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="B113" s="21">
+      <c r="A113" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B113" s="20">
         <v>0.05</v>
       </c>
-      <c r="C113" s="21">
+      <c r="C113" s="20">
         <v>0.15</v>
       </c>
-      <c r="D113" s="21">
+      <c r="D113" s="20">
         <v>0.35</v>
       </c>
-      <c r="E113" s="21">
+      <c r="E113" s="20">
         <v>0.25</v>
       </c>
-      <c r="F113" s="21">
+      <c r="F113" s="20">
         <v>0.2</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="20" t="s">
-        <v>48</v>
+      <c r="A114" s="19" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B79:L79"/>
-    <mergeCell ref="B86:J86"/>
-    <mergeCell ref="A108:L108"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A88:J88"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A87:C87"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="A106:C106"/>
-    <mergeCell ref="B98:I98"/>
-    <mergeCell ref="B105:J105"/>
+    <mergeCell ref="A51:L51"/>
+    <mergeCell ref="B43:J43"/>
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="B67:K67"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A69:C69"/>
     <mergeCell ref="A71:L71"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="B1:H1"/>
@@ -3452,12 +3451,17 @@
     <mergeCell ref="A37:L37"/>
     <mergeCell ref="A59:C59"/>
     <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A51:L51"/>
-    <mergeCell ref="B43:J43"/>
-    <mergeCell ref="A44:L44"/>
-    <mergeCell ref="B67:K67"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="B79:L79"/>
+    <mergeCell ref="B86:J86"/>
+    <mergeCell ref="A108:L108"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A88:J88"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A87:C87"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="A106:C106"/>
+    <mergeCell ref="B98:I98"/>
+    <mergeCell ref="B105:J105"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations xWindow="456" yWindow="628" count="12">
@@ -3517,460 +3521,460 @@
   <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" style="9" customWidth="1"/>
-    <col min="2" max="5" width="14.7109375" style="9" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="9"/>
-    <col min="8" max="8" width="41.85546875" style="9" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="9"/>
+    <col min="1" max="1" width="32.7109375" style="8" customWidth="1"/>
+    <col min="2" max="5" width="14.7109375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="8"/>
+    <col min="8" max="8" width="41.85546875" style="8" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="38"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="39"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="38"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="14"/>
+      <c r="B19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="39"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
-      <c r="B19" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B21" s="26">
+      <c r="B21" s="25">
         <v>0</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="25">
         <v>0</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="25">
         <v>1</v>
       </c>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="B22" s="26">
+      <c r="A22" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="25">
         <v>0.2</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="25">
         <v>0.1</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="25">
         <v>0.7</v>
       </c>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="B23" s="26">
+      <c r="A23" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="25">
         <v>0.3</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="25">
         <v>0.3</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="25">
         <v>0.4</v>
       </c>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" s="26">
+      <c r="A24" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="25">
         <v>0</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="25">
         <v>0</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="25">
         <v>0</v>
       </c>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="B25" s="26">
+      <c r="A25" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="25">
         <v>0</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="25">
         <v>0</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="25">
         <v>0</v>
       </c>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>48</v>
+      <c r="A26" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>123</v>
+      <c r="B27" s="9" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
-        <v>157</v>
-      </c>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
+      <c r="A28" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="37" t="s">
+      <c r="A29" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="B29" s="37"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="37"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="B30" s="33"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="27" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
+      <c r="B34" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
+      <c r="A35" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
+      <c r="A36" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
+      <c r="A37" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
-        <v>48</v>
+      <c r="A38" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -4007,180 +4011,180 @@
   <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="20.7109375" style="9" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="9"/>
+    <col min="1" max="4" width="20.7109375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="9"/>
+      <c r="B10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B12" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="D12" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
-      <c r="B10" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C12" s="6" t="s">
+      <c r="B13" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>165</v>
+      <c r="E13" s="5" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>48</v>
+      <c r="A14" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
